--- a/src/test/java/yatra/testdata/DemoTestData.xlsx
+++ b/src/test/java/yatra/testdata/DemoTestData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16815" windowHeight="6600" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16815" windowHeight="6600" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="All Testcases" sheetId="3" r:id="rId1"/>

--- a/src/test/java/yatra/testdata/DemoTestData.xlsx
+++ b/src/test/java/yatra/testdata/DemoTestData.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Journey" sheetId="1" r:id="rId3"/>
     <sheet name="Travellers" sheetId="5" r:id="rId4"/>
     <sheet name="Filters" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="300">
   <si>
     <t>TC_ID</t>
   </si>
@@ -804,9 +805,6 @@
     <t>Sydney</t>
   </si>
   <si>
-    <t>today</t>
-  </si>
-  <si>
     <t>RoundTrip_International</t>
   </si>
   <si>
@@ -868,13 +866,76 @@
   </si>
   <si>
     <t>FLDEMO02</t>
+  </si>
+  <si>
+    <t>ONEWAY</t>
+  </si>
+  <si>
+    <t>DOMESTIC</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>//p[@class='ow-price-above-btn']</t>
+  </si>
+  <si>
+    <t>//*[contains(@ng-show,'flt.totalFare')]</t>
+  </si>
+  <si>
+    <t>ROUND</t>
+  </si>
+  <si>
+    <t>//p[contains(@class,'total-fare')]/following-sibling::p</t>
+  </si>
+  <si>
+    <t>MULTICITY</t>
+  </si>
+  <si>
+    <t>MultiCity_International</t>
+  </si>
+  <si>
+    <t>tatalFareDomesticOneway</t>
+  </si>
+  <si>
+    <t>totalFareRoundMultiCity</t>
+  </si>
+  <si>
+    <t>tatalFareInternational</t>
+  </si>
+  <si>
+    <t>flightCards</t>
+  </si>
+  <si>
+    <t>//button[contains(text(),'View Fares')]/ancestor::div[contains(@class,'flight-det')]</t>
+  </si>
+  <si>
+    <t>//input[@type='radio']/ancestor::div[contains(@class,'flight-det')]</t>
+  </si>
+  <si>
+    <t>flightCardsTwoCards</t>
+  </si>
+  <si>
+    <t>//button[contains(text(),'Selected')]/ancestor::div[contains(@class,'flight-det')]</t>
+  </si>
+  <si>
+    <t>flightCardsSelectedButton</t>
+  </si>
+  <si>
+    <t>today+1</t>
+  </si>
+  <si>
+    <t>today+5</t>
+  </si>
+  <si>
+    <t>London</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -907,6 +968,17 @@
       <color rgb="FF262626"/>
       <name val="Rubik-Medium"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -928,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -943,6 +1015,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1273,7 +1349,7 @@
         <v>256</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1297,7 +1373,7 @@
         <v>256</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1305,7 +1381,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -1318,7 +1394,7 @@
         <v>search_multi_city_domestic_flight</v>
       </c>
       <c r="G4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1326,7 +1402,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>13</v>
@@ -1339,7 +1415,7 @@
         <v>search_multi_city_international_flight</v>
       </c>
       <c r="G5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1347,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
@@ -1363,7 +1439,7 @@
         <v>256</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1983,7 +2059,7 @@
         <v>65</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>13</v>
@@ -2091,7 +2167,7 @@
         <v>72</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s">
@@ -2107,7 +2183,7 @@
         <v>73</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s">
@@ -2885,7 +2961,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>245</v>
@@ -2900,7 +2976,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>246</v>
@@ -3038,7 +3114,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -3141,21 +3217,21 @@
         <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -3167,13 +3243,13 @@
         <v>257</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -3181,25 +3257,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D6" t="s">
         <v>275</v>
-      </c>
-      <c r="D6" t="s">
-        <v>276</v>
       </c>
       <c r="E6" t="s">
         <v>148</v>
       </c>
       <c r="F6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -3268,14 +3344,75 @@
         <v>252</v>
       </c>
     </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" t="s">
+        <v>297</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" t="s">
+        <v>298</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -3369,7 +3506,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -3386,7 +3523,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -3399,6 +3536,23 @@
       </c>
       <c r="E7" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3419,19 +3573,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3452,6 +3606,145 @@
     <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="9.140625" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
